--- a/data/gravel/Cotic Solaris 2025.xlsx
+++ b/data/gravel/Cotic Solaris 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372D9F8E-077F-9648-9AD2-69411311750C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77834F8-019C-CB46-BF4E-2B8197DFF381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8800" yWindow="540" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -272,9 +272,6 @@
     <t>fork</t>
   </si>
   <si>
-    <t>both</t>
-  </si>
-  <si>
     <t>yes</t>
   </si>
   <si>
@@ -408,6 +405,9 @@
   </si>
   <si>
     <t>100-130</t>
+  </si>
+  <si>
+    <t>flat bar</t>
   </si>
 </sst>
 </file>
@@ -772,7 +772,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -796,12 +796,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -809,7 +809,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -817,22 +817,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" t="s">
         <v>100</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>101</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>102</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>103</v>
-      </c>
-      <c r="G8" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -840,7 +840,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C9">
         <v>390</v>
@@ -858,7 +858,7 @@
         <v>495</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -935,7 +935,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <v>444</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>120</v>
@@ -1130,7 +1130,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C22">
         <v>0</v>
@@ -1281,22 +1281,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="C33" t="s">
+        <v>105</v>
+      </c>
+      <c r="D33" t="s">
         <v>106</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>107</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>108</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>109</v>
       </c>
-      <c r="G33" t="s">
-        <v>110</v>
-      </c>
       <c r="I33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -1307,22 +1307,22 @@
         <v>39</v>
       </c>
       <c r="C34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="G34" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I34" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
@@ -1330,25 +1330,25 @@
         <v>76</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G35" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I35" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
@@ -1356,25 +1356,25 @@
         <v>77</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="C36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G36" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="I36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.3">
@@ -1382,7 +1382,7 @@
         <v>78</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C37">
         <v>256</v>
@@ -1400,7 +1400,7 @@
         <v>364</v>
       </c>
       <c r="I37" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
@@ -1411,10 +1411,10 @@
         <v>41</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I38" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
@@ -1422,7 +1422,7 @@
         <v>42</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -1448,7 +1448,7 @@
         <v>46</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
@@ -1484,7 +1484,7 @@
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B49">
         <v>44</v>
@@ -1492,27 +1492,27 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B54" s="1"/>
     </row>
@@ -1575,7 +1575,7 @@
         <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
@@ -1583,7 +1583,7 @@
         <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
@@ -1662,7 +1662,7 @@
         <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
@@ -1670,15 +1670,15 @@
         <v>75</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
+        <v>84</v>
+      </c>
+      <c r="B79" t="s">
         <v>85</v>
-      </c>
-      <c r="B79" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
